--- a/output/2026-10-03_11_Malesia_Perak_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-03_11_Malesia_Perak_Utensilerie_e_Macchine_Utensili.xlsx
@@ -464,7 +464,6 @@
           <t>Asia-Mech Hydro-Pneumatic (M) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Perak (Ipoh)</t>
@@ -480,7 +479,6 @@
           <t>+60 5-282 1518</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Trader/distributore dal 1993 di sistemi elettro-pneumatici e idraulici, centraline custom, cilindri idraulici/pneumatici e componentistica (marchi ASR Hydraulic, CNF System, ASR Pneumatic). Indirizzo: 273, Jalan Lahat, Falim, 30200 Ipoh, Perak. Esistenza e contatti confermati tramite directory ufficiale MATRADE (Malaysia External Trade Development Corporation) e riscontro indipendente via ricerca web. Settore adiacente (componenti idraulici/pneumatici industriali) rispetto a utensileria manuale/macchine utensili tradizionali: valutare pertinenza esatta con il catalogo Dupuy. Email non reperita da fonte verificabile (lasciata vuota).</t>
@@ -498,7 +496,6 @@
           <t>Wah Seng Sin Kee Co Sdn Bhd</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Perak (Ipoh, con filiali a Kuala Lumpur, Kuantan, Butterworth)</t>
@@ -509,8 +506,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Grossista/rivenditore di hardware e utensili attivo dagli anni '50, con gamma di prodotti hardware/tools in espansione. Indirizzo: TBK 365, Jalan Menglembu, Ipoh, 31450 Perak. Esistenza confermata tramite jobstore.my (listing aziendale con settore Manufacturing/Production, 26-50 dipendenti). Nessun telefono/email reperibile da fonte verificata: lasciati vuoti. Sito web non trovato.</t>
@@ -518,7 +513,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -528,7 +523,6 @@
           <t>Banli Hardware Sdn Bhd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Perak (Ipoh)</t>
@@ -539,8 +533,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Grossista di hardware e materiali da costruzione, inclusi utensili (hardware tools); serve clienti, contractors e hardware businesses (rapporto B2B) nelle regioni Nord e Centro Malesia. Indirizzo: 14 &amp; 16, Jalan Kilang 2, Jelapang Light Industrial Estate, 30100 Ipoh, Perak. Esistenza confermata tramite jobstreet.my (11-50 dipendenti). Telefono/email non reperiti da fonte verificata: lasciati vuoti. Sito web non trovato.</t>
@@ -548,7 +540,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -578,7 +570,6 @@
           <t>+60 16-539 9373</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Rivenditore di hardware (utensili manuali ed elettrici, materiali edili, elettrico, vernici, DPI). Indirizzo: 95-96 Jalan Ampang, Tambun, 31400 Ipoh, Perak. Indirizzo e telefono confermati tramite leadstal.com. Natura prevalentemente retail/ferramenta di zona: non confermato con certezza l'orientamento B2B verso aziende (da verificare umanamente l'idoneita' come distributore). Il sito web indicato (thhardwarebuilding.com) non risulta raggiungibile/risolvibile al momento della verifica (DNS non risolve): dato riportato solo come riferimento dalla fonte, non verificato attivo. Email non reperita.</t>
@@ -586,7 +577,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
